--- a/request_forms/020_managed_security_services_pricing_request_form--request_forms.xlsx
+++ b/request_forms/020_managed_security_services_pricing_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'compliance_and_governance'}</t>
+          <t>compliance_and_governance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Compliance and Governance'}</t>
+          <t>Compliance and Governance</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cloud_security'}</t>
+          <t>cloud_security</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cloud Security'}</t>
+          <t>Cloud Security</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cyber_security_awareness'}</t>
+          <t>cyber_security_awareness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cyber Security Awareness'}</t>
+          <t>Cyber Security Awareness</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'identity_and_access_management'}</t>
+          <t>identity_and_access_management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Identity and Access Management'}</t>
+          <t>Identity and Access Management</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'incident_response'}</t>
+          <t>incident_response</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Incident Response'}</t>
+          <t>Incident Response</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'penetration_testing'}</t>
+          <t>penetration_testing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Penetration Testing'}</t>
+          <t>Penetration Testing</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'security_consulting'}</t>
+          <t>security_consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Security Consulting'}</t>
+          <t>Security Consulting</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'security_auditing'}</t>
+          <t>security_auditing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Security Auditing'}</t>
+          <t>Security Auditing</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'security_policy_development'}</t>
+          <t>security_policy_development</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Security Policy Development'}</t>
+          <t>Security Policy Development</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'vulnerability_management'}</t>
+          <t>vulnerability_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Vulnerability Management'}</t>
+          <t>Vulnerability Management</t>
         </is>
       </c>
     </row>
